--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-17047</t>
+          <t>I-84192</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.0367039</t>
+          <t>-6.0442072</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9809405</t>
+          <t>-76.9719876</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jr. Miraflores</t>
+          <t>Jirón 20 de Abril / Jirón Pucallpa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-294439</t>
+          <t>I-295434</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.0311943</t>
+          <t>-6.0384638</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9809044</t>
+          <t>-76.9799664</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Ramón Castilla / Jr. Trujillo</t>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-564870</t>
+          <t>I-17047</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.0368535</t>
+          <t>-6.0367039</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9803605</t>
+          <t>-76.9809405</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jr. Miraflores</t>
+          <t>Jirón Miraflores / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-84192</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.0442072</t>
+          <t>-6.0545297</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.9719876</t>
+          <t>-76.996806</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jr. 20 de Abril / Jr. Pucallpa</t>
+          <t>To Alfarillo / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-84205</t>
+          <t>I-755481</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.044127</t>
+          <t>-5.6335633</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-76.9719754</t>
+          <t>-77.6167623</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jr. 20 de Abril / Jr. Pucallpa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-84337</t>
+          <t>I-755486</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.0346881</t>
+          <t>-5.6527307</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-76.9727889</t>
+          <t>-77.5821903</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jr. Callao / Jr. Reyes Guerra</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-84387</t>
+          <t>I-17064</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,25 +820,493 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.0352848</t>
+          <t>-6.0414531</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.9782283</t>
+          <t>-76.981391</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jr. Damián Nájar / Jr. Sargento Tejada</t>
+          <t>Calle Señor de los Milagros / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-17078</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-6.038742</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-76.9854311</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-17081</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-6.0383728</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-76.9831655</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-84559</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-6.0316842</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-76.9860962</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-6.0486163</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-76.9913323</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-577630</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-5.8725422</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-77.1875328</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-577645</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-5.8762936</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-77.1868408</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-577644</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-5.8737616</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-77.1858444</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-577637</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-5.8764004</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-77.1850893</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-577636</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-5.8772715</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-77.1843288</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>220101</t>
         </is>

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
+          <t>Jirón Bella Aurora / Vía de Evitamiento Indañe-Shango</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-84192</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.0442072</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-295434</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.0384638</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-17047</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.0367039</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.0545297</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-755481</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-5.6335633</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-755486</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-5.6527307</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-17064</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.0414531</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-17078</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.038742</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-17081</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.0383728</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-84559</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.0316842</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-4</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.0486163</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-577630</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-5.8725422</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-577645</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-5.8762936</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-577644</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-5.8737616</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-577637</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-5.8764004</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAN_MARTIN</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-577636</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>220101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MOYOBAMBA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-5.8772715</t>
@@ -1304,11 +1224,6 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>220101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -1222,6 +1210,711 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>I-17039</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-6.0344929</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-76.9684862</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Jr. Coronel Secada con Calle Pedro Orbe</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>I-84335</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-6.0348801</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-76.9719347</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Jr. Benavides con Jr. Callao</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>I-84339</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-6.0341578</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-76.9750469</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jr. San Martin con Jr. Callao</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>I-84340</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-6.0355696</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-76.9698332</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Jr. 20 de abril con Jr. Callao</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>I-84360</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-6.0255717</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-76.98535</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Jr. Rioja con Dos de Mayo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>I-84387</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6.0352848</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-76.9782283</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jr. Sargento Tejada con Jr. Damian Najar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>I-84409</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-6.0334754</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-76.9619619</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Jr. Libertad con Jr. Jesus Alberto Miranda</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I-84411</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-6.0294254</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-76.9700129</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jr. Benavides con Jr.Emilio San Martin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>I-84416</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-6.0300677</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-76.9681549</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Jr. Emilio San Martin con Jr. 20 de Abril</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I-84424</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-6.0335042</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-76.9715866</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jr. Benavides con Serafin Filomeno</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>I-84431</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-6.0325259</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-76.9653997</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Jr. Libertad con Jr. Miguel Grau</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I-84541</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-6.037921</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-76.9668991</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Jr. Coronel Bardales con Jr.Manuel del Aguila</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>I-294437</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-6.0300087</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-76.9740538</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Jr. Dos de Mayo con Jr. San Martin</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>I-418851</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-6.0337777</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-76.9705736</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Jiron Varacadillo con Jr. Serafin Filomeno</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MOYOBAMBA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>I-491996</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-6.0276539</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-76.9818381</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jr. Dos de Mayo con Jr. Vicente Najar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
+++ b/Intersecciones/excels/SAN_MARTIN-MOYOBAMBA-MOYOBAMBA.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-84192</t>
+          <t>I-84559</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.0442072</t>
+          <t>-6.0316842</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-76.9719876</t>
+          <t>-76.9860962</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón 20 de Abril / Jirón Pucallpa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-295434</t>
+          <t>I-84541</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.0384638</t>
+          <t>-6.037921</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-76.9799664</t>
+          <t>-76.9668991</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jirón Bella Aurora / Vía de Evitamiento Indañe-Shango</t>
+          <t>Jr. Coronel Bardales con Jr.Manuel del Aguila</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-17047</t>
+          <t>I-84431</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.0367039</t>
+          <t>-6.0325259</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-76.9809405</t>
+          <t>-76.9653997</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jirón Miraflores / Calle s / n</t>
+          <t>Jr. Libertad con Jr. Miguel Grau</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-84424</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.0545297</t>
+          <t>-6.0335042</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-76.996806</t>
+          <t>-76.9715866</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>To Alfarillo / Calle s / n</t>
+          <t>Jr. Benavides con Serafin Filomeno</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-755481</t>
+          <t>I-84416</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.6335633</t>
+          <t>-6.0300677</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-77.6167623</t>
+          <t>-76.9681549</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Emilio San Martin con Jr. 20 de Abril</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-755486</t>
+          <t>I-84411</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.6527307</t>
+          <t>-6.0294254</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-77.5821903</t>
+          <t>-76.9700129</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Benavides con Jr.Emilio San Martin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-17064</t>
+          <t>I-84409</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.0414531</t>
+          <t>-6.0334754</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-76.981391</t>
+          <t>-76.9619619</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle Señor de los Milagros / Calle s / n</t>
+          <t>Jr. Libertad con Jr. Jesus Alberto Miranda</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-17078</t>
+          <t>I-84387</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.038742</t>
+          <t>-6.0352848</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-76.9854311</t>
+          <t>-76.9782283</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
+          <t>Jr. Sargento Tejada con Jr. Damian Najar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,22 +862,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-17081</t>
+          <t>I-84360</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.0383728</t>
+          <t>-6.0255717</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-76.9831655</t>
+          <t>-76.98535</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
+          <t>Jr. Rioja con Dos de Mayo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-84559</t>
+          <t>I-84340</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.0316842</t>
+          <t>-6.0355696</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-76.9860962</t>
+          <t>-76.9698332</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. 20 de abril con Jr. Callao</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-84339</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.0486163</t>
+          <t>-6.0341578</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-76.9913323</t>
+          <t>-76.9750469</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. San Martin con Jr. Callao</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-577630</t>
+          <t>I-84335</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.8725422</t>
+          <t>-6.0348801</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-77.1875328</t>
+          <t>-76.9719347</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Benavides con Jr. Callao</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-577645</t>
+          <t>I-84192</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.8762936</t>
+          <t>-6.0442072</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-77.1868408</t>
+          <t>-76.9719876</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón 20 de Abril / Jirón Pucallpa</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-577644</t>
+          <t>I-755486</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.8737616</t>
+          <t>-5.6527307</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-77.1858444</t>
+          <t>-77.5821903</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-577637</t>
+          <t>I-755481</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.8764004</t>
+          <t>-5.6335633</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-77.1850893</t>
+          <t>-77.6167623</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-577636</t>
+          <t>I-577645</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.8772715</t>
+          <t>-5.8762936</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-77.1843288</t>
+          <t>-77.1868408</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-17039</t>
+          <t>I-577644</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.0344929</t>
+          <t>-5.8737616</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-76.9684862</t>
+          <t>-77.1858444</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jr. Coronel Secada con Calle Pedro Orbe</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-84335</t>
+          <t>I-577637</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.0348801</t>
+          <t>-5.8764004</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-76.9719347</t>
+          <t>-77.1850893</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jr. Benavides con Jr. Callao</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-84339</t>
+          <t>I-577636</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.0341578</t>
+          <t>-5.8772715</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-76.9750469</t>
+          <t>-77.1843288</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jr. San Martin con Jr. Callao</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-84340</t>
+          <t>I-577630</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.0355696</t>
+          <t>-5.8725422</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-76.9698332</t>
+          <t>-77.1875328</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jr. 20 de abril con Jr. Callao</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-84360</t>
+          <t>I-491996</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.0255717</t>
+          <t>-6.0276539</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-76.98535</t>
+          <t>-76.9818381</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jr. Rioja con Dos de Mayo</t>
+          <t>Jr. Dos de Mayo con Jr. Vicente Najar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-84387</t>
+          <t>I-418851</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.0352848</t>
+          <t>-6.0337777</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-76.9782283</t>
+          <t>-76.9705736</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jr. Sargento Tejada con Jr. Damian Najar</t>
+          <t>Jiron Varacadillo con Jr. Serafin Filomeno</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-84409</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.0334754</t>
+          <t>-6.0486163</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-76.9619619</t>
+          <t>-76.9913323</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jr. Libertad con Jr. Jesus Alberto Miranda</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-84411</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.0294254</t>
+          <t>-6.0545297</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-76.9700129</t>
+          <t>-76.996806</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jr. Benavides con Jr.Emilio San Martin</t>
+          <t>To Alfarillo / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-84416</t>
+          <t>I-295434</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.0300677</t>
+          <t>-6.0384638</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-76.9681549</t>
+          <t>-76.9799664</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jr. Emilio San Martin con Jr. 20 de Abril</t>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-84424</t>
+          <t>I-294437</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.0335042</t>
+          <t>-6.0300087</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-76.9715866</t>
+          <t>-76.9740538</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Jr. Benavides con Serafin Filomeno</t>
+          <t>Jr. Dos de Mayo con Jr. San Martin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-84431</t>
+          <t>I-17081</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.0325259</t>
+          <t>-6.0383728</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-76.9653997</t>
+          <t>-76.9831655</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Jr. Libertad con Jr. Miguel Grau</t>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-84541</t>
+          <t>I-17078</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.037921</t>
+          <t>-6.038742</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-76.9668991</t>
+          <t>-76.9854311</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Jr. Coronel Bardales con Jr.Manuel del Aguila</t>
+          <t>Vía de Evitamiento Indañe-Shango / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-294437</t>
+          <t>I-17064</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.0300087</t>
+          <t>-6.0414531</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-76.9740538</t>
+          <t>-76.981391</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jr. Dos de Mayo con Jr. San Martin</t>
+          <t>Calle Señor de los Milagros / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-418851</t>
+          <t>I-17047</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.0337777</t>
+          <t>-6.0367039</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-76.9705736</t>
+          <t>-76.9809405</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Jiron Varacadillo con Jr. Serafin Filomeno</t>
+          <t>Jirón Miraflores / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-491996</t>
+          <t>I-17039</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-6.0276539</t>
+          <t>-6.0344929</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-76.9818381</t>
+          <t>-76.9684862</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Jr. Dos de Mayo con Jr. Vicente Najar</t>
+          <t>Jr. Coronel Secada con Calle Pedro Orbe</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
